--- a/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2023/WISCONSIN_2023.xlsx
+++ b/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2023/WISCONSIN_2023.xlsx
@@ -2364,7 +2364,7 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Cuatro Cienegas</t>
+          <t>Cuatrocienegas</t>
         </is>
       </c>
       <c r="C112">
@@ -4578,7 +4578,7 @@
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>Dolores Hidalgo Cuna De La Independencia Nacional</t>
+          <t>Dolores Hidalgo</t>
         </is>
       </c>
       <c r="C235">
